--- a/프로젝트관리.xlsx
+++ b/프로젝트관리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ra_react\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F4BCBB-117E-429A-980B-9C84ECFDF855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDD16A7-1877-4CBD-A8FB-BA5C322F4C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1665" windowWidth="19230" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8880" yWindow="780" windowWidth="19230" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="프로젝트 플래너" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>오른쪽에서 강조 표시할 기간을 선택합니다.  그 다음, 차트를 설명하는 범례가 나옵니다.</t>
   </si>
@@ -162,26 +162,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>프로젝트관리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MES</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시보드 차트(Chart.js, Recharts 등)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>공정 관리 및 재고 현황 테이블</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사용자 권한별 화면 제어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">이력서/포트폴리오 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -210,10 +194,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">디자인 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>UI/UX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -222,10 +202,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 개선 포인트(리팩토링 대상) 정리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 기간 강조 표시:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -234,27 +210,71 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PLASTIC</t>
+    <t>비밀번호찾기/이메일전송…</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>상담 게시판</t>
+    <t>MES 프로젝트관리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사용자 예약 시스템 / 예약리스트 예약폼</t>
+    <t>프로젝트 기반 구축</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TanStack Query/table</t>
+    <t>Axios/TanStack-Query &amp; 웹소켓</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>관리자캘린더/ 예약리스트(TanStack table)</t>
+    <t>실시간 센서/생산 추이 차트</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>비밀번호찾기/이메일전송…</t>
+    <t>실시간 대시보드(공장 통합 현황판)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대용량 목록 조회 &amp; 검색 기능(TanStack table)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공통 UI(버튼,팝업창,input, table)  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실시간 데이터 모니터링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">핵심 생산 지표(KPI)요약 카드 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장 도면 기반 위에 가동/정지 상태 시각화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MES 공정 및 시스템관리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 권한별(작업자/관리자) 접근 메뉴 제어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디자인 애니메이션 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이드바,header,footer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이아웃 및 theme 테마 및 전역 스타일 설정 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 및 관리자모드 경로별 레이아웃 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -266,7 +286,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -366,8 +386,22 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,6 +440,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,7 +593,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -623,9 +663,6 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -661,6 +698,36 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="8" borderId="0" xfId="6" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="8" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1071,11 +1138,11 @@
     <tabColor theme="7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BO37"/>
+  <dimension ref="B1:BO42"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="2" width="43.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="51" style="2" customWidth="1"/>
     <col min="3" max="6" width="15.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="1" customWidth="1"/>
@@ -1085,7 +1152,7 @@
   <sheetData>
     <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1">
       <c r="B1" s="7" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -1154,63 +1221,63 @@
       <c r="BO1" s="10"/>
     </row>
     <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
       <c r="G2" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H2" s="12">
         <v>1</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="13"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="34"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="33"/>
       <c r="P2" s="14"/>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="34"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="33"/>
       <c r="U2" s="15"/>
-      <c r="V2" s="24" t="s">
+      <c r="V2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="35"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="34"/>
       <c r="Z2" s="16"/>
-      <c r="AA2" s="24" t="s">
+      <c r="AA2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="35"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="34"/>
       <c r="AH2" s="17"/>
-      <c r="AI2" s="24" t="s">
+      <c r="AI2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="24"/>
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
       <c r="AQ2" s="10"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="10"/>
@@ -1238,22 +1305,22 @@
       <c r="BO2" s="10"/>
     </row>
     <row r="3" spans="2:67" s="4" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="30" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="18" t="s">
@@ -1320,12 +1387,12 @@
       <c r="BO3" s="21"/>
     </row>
     <row r="4" spans="2:67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="28"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="22">
         <v>1</v>
       </c>
@@ -1507,87 +1574,90 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="5">
+    <row r="5" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="36">
         <v>16</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="36">
         <v>5</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="36">
         <v>18</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="36">
         <v>10</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="37">
         <v>0.85</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10"/>
-      <c r="AF5" s="10"/>
-      <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
-      <c r="AJ5" s="10"/>
-      <c r="AK5" s="10"/>
-      <c r="AL5" s="10"/>
-      <c r="AM5" s="10"/>
-      <c r="AN5" s="10"/>
-      <c r="AO5" s="10"/>
-      <c r="AP5" s="10"/>
-      <c r="AQ5" s="10"/>
-      <c r="AR5" s="10"/>
-      <c r="AS5" s="10"/>
-      <c r="AT5" s="10"/>
-      <c r="AU5" s="10"/>
-      <c r="AV5" s="10"/>
-      <c r="AW5" s="10"/>
-      <c r="AX5" s="10"/>
-      <c r="AY5" s="10"/>
-      <c r="AZ5" s="10"/>
-      <c r="BA5" s="10"/>
-      <c r="BB5" s="10"/>
-      <c r="BC5" s="10"/>
-      <c r="BD5" s="10"/>
-      <c r="BE5" s="10"/>
-      <c r="BF5" s="10"/>
-      <c r="BG5" s="10"/>
-      <c r="BH5" s="10"/>
-      <c r="BI5" s="10"/>
-      <c r="BJ5" s="10"/>
-      <c r="BK5" s="10"/>
-      <c r="BL5" s="10"/>
-      <c r="BM5" s="10"/>
-      <c r="BN5" s="10"/>
-      <c r="BO5" s="10"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="38"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="39"/>
+      <c r="AQ5" s="39"/>
+      <c r="AR5" s="39"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="39"/>
+      <c r="AU5" s="39"/>
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="39"/>
+      <c r="AX5" s="39"/>
+      <c r="AY5" s="39"/>
+      <c r="AZ5" s="39"/>
+      <c r="BA5" s="39"/>
+      <c r="BB5" s="39"/>
+      <c r="BC5" s="39"/>
+      <c r="BD5" s="39"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="39"/>
+      <c r="BG5" s="39"/>
+      <c r="BH5" s="39"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="39"/>
+      <c r="BK5" s="39"/>
+      <c r="BL5" s="39"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
+      <c r="BO5" s="39"/>
     </row>
     <row r="6" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C6" s="5">
         <v>2</v>
       </c>
@@ -1658,15 +1728,11 @@
       <c r="BO6" s="10"/>
     </row>
     <row r="7" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="5">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5">
-        <v>3</v>
-      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="H7" s="9"/>
@@ -1732,14 +1798,10 @@
     </row>
     <row r="8" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5">
-        <v>3</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="H8" s="9"/>
@@ -1874,7 +1936,7 @@
     </row>
     <row r="10" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1942,7 +2004,7 @@
       <c r="BO10" s="10"/>
     </row>
     <row r="11" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2007,81 +2069,90 @@
       <c r="BN11" s="10"/>
       <c r="BO11" s="10"/>
     </row>
-    <row r="12" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
-      <c r="AJ12" s="10"/>
-      <c r="AK12" s="10"/>
-      <c r="AL12" s="10"/>
-      <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="10"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="10"/>
-      <c r="AR12" s="10"/>
-      <c r="AS12" s="10"/>
-      <c r="AT12" s="10"/>
-      <c r="AU12" s="10"/>
-      <c r="AV12" s="10"/>
-      <c r="AW12" s="10"/>
-      <c r="AX12" s="10"/>
-      <c r="AY12" s="10"/>
-      <c r="AZ12" s="10"/>
-      <c r="BA12" s="10"/>
-      <c r="BB12" s="10"/>
-      <c r="BC12" s="10"/>
-      <c r="BD12" s="10"/>
-      <c r="BE12" s="10"/>
-      <c r="BF12" s="10"/>
-      <c r="BG12" s="10"/>
-      <c r="BH12" s="10"/>
-      <c r="BI12" s="10"/>
-      <c r="BJ12" s="10"/>
-      <c r="BK12" s="10"/>
-      <c r="BL12" s="10"/>
-      <c r="BM12" s="10"/>
-      <c r="BN12" s="10"/>
-      <c r="BO12" s="10"/>
+    <row r="12" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="36">
+        <v>3</v>
+      </c>
+      <c r="D12" s="36">
+        <v>3</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="39"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="39"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="39"/>
+      <c r="AN12" s="39"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="39"/>
+      <c r="AQ12" s="39"/>
+      <c r="AR12" s="39"/>
+      <c r="AS12" s="39"/>
+      <c r="AT12" s="39"/>
+      <c r="AU12" s="39"/>
+      <c r="AV12" s="39"/>
+      <c r="AW12" s="39"/>
+      <c r="AX12" s="39"/>
+      <c r="AY12" s="39"/>
+      <c r="AZ12" s="39"/>
+      <c r="BA12" s="39"/>
+      <c r="BB12" s="39"/>
+      <c r="BC12" s="39"/>
+      <c r="BD12" s="39"/>
+      <c r="BE12" s="39"/>
+      <c r="BF12" s="39"/>
+      <c r="BG12" s="39"/>
+      <c r="BH12" s="39"/>
+      <c r="BI12" s="39"/>
+      <c r="BJ12" s="39"/>
+      <c r="BK12" s="39"/>
+      <c r="BL12" s="39"/>
+      <c r="BM12" s="39"/>
+      <c r="BN12" s="39"/>
+      <c r="BO12" s="39"/>
     </row>
     <row r="13" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="H13" s="9"/>
@@ -2147,7 +2218,7 @@
     </row>
     <row r="14" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2216,7 +2287,7 @@
     </row>
     <row r="15" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2284,10 +2355,7 @@
       <c r="BO15" s="10"/>
     </row>
     <row r="16" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2352,75 +2420,79 @@
       <c r="BN16" s="10"/>
       <c r="BO16" s="10"/>
     </row>
-    <row r="17" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="10"/>
-      <c r="AI17" s="10"/>
-      <c r="AJ17" s="10"/>
-      <c r="AK17" s="10"/>
-      <c r="AL17" s="10"/>
-      <c r="AM17" s="10"/>
-      <c r="AN17" s="10"/>
-      <c r="AO17" s="10"/>
-      <c r="AP17" s="10"/>
-      <c r="AQ17" s="10"/>
-      <c r="AR17" s="10"/>
-      <c r="AS17" s="10"/>
-      <c r="AT17" s="10"/>
-      <c r="AU17" s="10"/>
-      <c r="AV17" s="10"/>
-      <c r="AW17" s="10"/>
-      <c r="AX17" s="10"/>
-      <c r="AY17" s="10"/>
-      <c r="AZ17" s="10"/>
-      <c r="BA17" s="10"/>
-      <c r="BB17" s="10"/>
-      <c r="BC17" s="10"/>
-      <c r="BD17" s="10"/>
-      <c r="BE17" s="10"/>
-      <c r="BF17" s="10"/>
-      <c r="BG17" s="10"/>
-      <c r="BH17" s="10"/>
-      <c r="BI17" s="10"/>
-      <c r="BJ17" s="10"/>
-      <c r="BK17" s="10"/>
-      <c r="BL17" s="10"/>
-      <c r="BM17" s="10"/>
-      <c r="BN17" s="10"/>
-      <c r="BO17" s="10"/>
+    <row r="17" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="38"/>
+      <c r="AA17" s="38"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="39"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="39"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
+      <c r="AJ17" s="39"/>
+      <c r="AK17" s="39"/>
+      <c r="AL17" s="39"/>
+      <c r="AM17" s="39"/>
+      <c r="AN17" s="39"/>
+      <c r="AO17" s="39"/>
+      <c r="AP17" s="39"/>
+      <c r="AQ17" s="39"/>
+      <c r="AR17" s="39"/>
+      <c r="AS17" s="39"/>
+      <c r="AT17" s="39"/>
+      <c r="AU17" s="39"/>
+      <c r="AV17" s="39"/>
+      <c r="AW17" s="39"/>
+      <c r="AX17" s="39"/>
+      <c r="AY17" s="39"/>
+      <c r="AZ17" s="39"/>
+      <c r="BA17" s="39"/>
+      <c r="BB17" s="39"/>
+      <c r="BC17" s="39"/>
+      <c r="BD17" s="39"/>
+      <c r="BE17" s="39"/>
+      <c r="BF17" s="39"/>
+      <c r="BG17" s="39"/>
+      <c r="BH17" s="39"/>
+      <c r="BI17" s="39"/>
+      <c r="BJ17" s="39"/>
+      <c r="BK17" s="39"/>
+      <c r="BL17" s="39"/>
+      <c r="BM17" s="39"/>
+      <c r="BN17" s="39"/>
+      <c r="BO17" s="39"/>
     </row>
     <row r="18" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="23" t="s">
-        <v>25</v>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -2489,7 +2561,7 @@
     </row>
     <row r="19" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -2558,7 +2630,7 @@
     </row>
     <row r="20" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -2626,6 +2698,9 @@
       <c r="BO20" s="10"/>
     </row>
     <row r="21" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -2692,9 +2767,6 @@
       <c r="BO21" s="10"/>
     </row>
     <row r="22" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
-        <v>18</v>
-      </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -2760,78 +2832,79 @@
       <c r="BN22" s="10"/>
       <c r="BO22" s="10"/>
     </row>
-    <row r="23" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
-      <c r="AI23" s="10"/>
-      <c r="AJ23" s="10"/>
-      <c r="AK23" s="10"/>
-      <c r="AL23" s="10"/>
-      <c r="AM23" s="10"/>
-      <c r="AN23" s="10"/>
-      <c r="AO23" s="10"/>
-      <c r="AP23" s="10"/>
-      <c r="AQ23" s="10"/>
-      <c r="AR23" s="10"/>
-      <c r="AS23" s="10"/>
-      <c r="AT23" s="10"/>
-      <c r="AU23" s="10"/>
-      <c r="AV23" s="10"/>
-      <c r="AW23" s="10"/>
-      <c r="AX23" s="10"/>
-      <c r="AY23" s="10"/>
-      <c r="AZ23" s="10"/>
-      <c r="BA23" s="10"/>
-      <c r="BB23" s="10"/>
-      <c r="BC23" s="10"/>
-      <c r="BD23" s="10"/>
-      <c r="BE23" s="10"/>
-      <c r="BF23" s="10"/>
-      <c r="BG23" s="10"/>
-      <c r="BH23" s="10"/>
-      <c r="BI23" s="10"/>
-      <c r="BJ23" s="10"/>
-      <c r="BK23" s="10"/>
-      <c r="BL23" s="10"/>
-      <c r="BM23" s="10"/>
-      <c r="BN23" s="10"/>
-      <c r="BO23" s="10"/>
+    <row r="23" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="39"/>
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
+      <c r="AJ23" s="39"/>
+      <c r="AK23" s="39"/>
+      <c r="AL23" s="39"/>
+      <c r="AM23" s="39"/>
+      <c r="AN23" s="39"/>
+      <c r="AO23" s="39"/>
+      <c r="AP23" s="39"/>
+      <c r="AQ23" s="39"/>
+      <c r="AR23" s="39"/>
+      <c r="AS23" s="39"/>
+      <c r="AT23" s="39"/>
+      <c r="AU23" s="39"/>
+      <c r="AV23" s="39"/>
+      <c r="AW23" s="39"/>
+      <c r="AX23" s="39"/>
+      <c r="AY23" s="39"/>
+      <c r="AZ23" s="39"/>
+      <c r="BA23" s="39"/>
+      <c r="BB23" s="39"/>
+      <c r="BC23" s="39"/>
+      <c r="BD23" s="39"/>
+      <c r="BE23" s="39"/>
+      <c r="BF23" s="39"/>
+      <c r="BG23" s="39"/>
+      <c r="BH23" s="39"/>
+      <c r="BI23" s="39"/>
+      <c r="BJ23" s="39"/>
+      <c r="BK23" s="39"/>
+      <c r="BL23" s="39"/>
+      <c r="BM23" s="39"/>
+      <c r="BN23" s="39"/>
+      <c r="BO23" s="39"/>
     </row>
     <row r="24" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2899,6 +2972,9 @@
       <c r="BO24" s="10"/>
     </row>
     <row r="25" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2965,9 +3041,6 @@
       <c r="BO25" s="10"/>
     </row>
     <row r="26" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -3033,73 +3106,80 @@
       <c r="BN26" s="10"/>
       <c r="BO26" s="10"/>
     </row>
-    <row r="27" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="10"/>
-      <c r="AC27" s="10"/>
-      <c r="AD27" s="10"/>
-      <c r="AE27" s="10"/>
-      <c r="AF27" s="10"/>
-      <c r="AG27" s="10"/>
-      <c r="AH27" s="10"/>
-      <c r="AI27" s="10"/>
-      <c r="AJ27" s="10"/>
-      <c r="AK27" s="10"/>
-      <c r="AL27" s="10"/>
-      <c r="AM27" s="10"/>
-      <c r="AN27" s="10"/>
-      <c r="AO27" s="10"/>
-      <c r="AP27" s="10"/>
-      <c r="AQ27" s="10"/>
-      <c r="AR27" s="10"/>
-      <c r="AS27" s="10"/>
-      <c r="AT27" s="10"/>
-      <c r="AU27" s="10"/>
-      <c r="AV27" s="10"/>
-      <c r="AW27" s="10"/>
-      <c r="AX27" s="10"/>
-      <c r="AY27" s="10"/>
-      <c r="AZ27" s="10"/>
-      <c r="BA27" s="10"/>
-      <c r="BB27" s="10"/>
-      <c r="BC27" s="10"/>
-      <c r="BD27" s="10"/>
-      <c r="BE27" s="10"/>
-      <c r="BF27" s="10"/>
-      <c r="BG27" s="10"/>
-      <c r="BH27" s="10"/>
-      <c r="BI27" s="10"/>
-      <c r="BJ27" s="10"/>
-      <c r="BK27" s="10"/>
-      <c r="BL27" s="10"/>
-      <c r="BM27" s="10"/>
-      <c r="BN27" s="10"/>
-      <c r="BO27" s="10"/>
+    <row r="27" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="38"/>
+      <c r="Y27" s="38"/>
+      <c r="Z27" s="38"/>
+      <c r="AA27" s="38"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="39"/>
+      <c r="AF27" s="39"/>
+      <c r="AG27" s="39"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="39"/>
+      <c r="AJ27" s="39"/>
+      <c r="AK27" s="39"/>
+      <c r="AL27" s="39"/>
+      <c r="AM27" s="39"/>
+      <c r="AN27" s="39"/>
+      <c r="AO27" s="39"/>
+      <c r="AP27" s="39"/>
+      <c r="AQ27" s="39"/>
+      <c r="AR27" s="39"/>
+      <c r="AS27" s="39"/>
+      <c r="AT27" s="39"/>
+      <c r="AU27" s="39"/>
+      <c r="AV27" s="39"/>
+      <c r="AW27" s="39"/>
+      <c r="AX27" s="39"/>
+      <c r="AY27" s="39"/>
+      <c r="AZ27" s="39"/>
+      <c r="BA27" s="39"/>
+      <c r="BB27" s="39"/>
+      <c r="BC27" s="39"/>
+      <c r="BD27" s="39"/>
+      <c r="BE27" s="39"/>
+      <c r="BF27" s="39"/>
+      <c r="BG27" s="39"/>
+      <c r="BH27" s="39"/>
+      <c r="BI27" s="39"/>
+      <c r="BJ27" s="39"/>
+      <c r="BK27" s="39"/>
+      <c r="BL27" s="39"/>
+      <c r="BM27" s="39"/>
+      <c r="BN27" s="39"/>
+      <c r="BO27" s="39"/>
     </row>
     <row r="28" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -3166,6 +3246,9 @@
       <c r="BO28" s="10"/>
     </row>
     <row r="29" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -3297,29 +3380,323 @@
       <c r="BN30" s="10"/>
       <c r="BO30" s="10"/>
     </row>
-    <row r="32" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="2" t="s">
+    <row r="31" spans="2:67" s="44" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
+      <c r="X31" s="43"/>
+      <c r="Y31" s="43"/>
+      <c r="Z31" s="43"/>
+      <c r="AA31" s="43"/>
+    </row>
+    <row r="32" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="10"/>
+      <c r="AC32" s="10"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
+      <c r="AH32" s="10"/>
+      <c r="AI32" s="10"/>
+      <c r="AJ32" s="10"/>
+      <c r="AK32" s="10"/>
+      <c r="AL32" s="10"/>
+      <c r="AM32" s="10"/>
+      <c r="AN32" s="10"/>
+      <c r="AO32" s="10"/>
+      <c r="AP32" s="10"/>
+      <c r="AQ32" s="10"/>
+      <c r="AR32" s="10"/>
+      <c r="AS32" s="10"/>
+      <c r="AT32" s="10"/>
+      <c r="AU32" s="10"/>
+      <c r="AV32" s="10"/>
+      <c r="AW32" s="10"/>
+      <c r="AX32" s="10"/>
+      <c r="AY32" s="10"/>
+      <c r="AZ32" s="10"/>
+      <c r="BA32" s="10"/>
+      <c r="BB32" s="10"/>
+      <c r="BC32" s="10"/>
+      <c r="BD32" s="10"/>
+      <c r="BE32" s="10"/>
+      <c r="BF32" s="10"/>
+      <c r="BG32" s="10"/>
+      <c r="BH32" s="10"/>
+      <c r="BI32" s="10"/>
+      <c r="BJ32" s="10"/>
+      <c r="BK32" s="10"/>
+      <c r="BL32" s="10"/>
+      <c r="BM32" s="10"/>
+      <c r="BN32" s="10"/>
+      <c r="BO32" s="10"/>
+    </row>
+    <row r="33" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="10"/>
+      <c r="AC33" s="10"/>
+      <c r="AD33" s="10"/>
+      <c r="AE33" s="10"/>
+      <c r="AF33" s="10"/>
+      <c r="AG33" s="10"/>
+      <c r="AH33" s="10"/>
+      <c r="AI33" s="10"/>
+      <c r="AJ33" s="10"/>
+      <c r="AK33" s="10"/>
+      <c r="AL33" s="10"/>
+      <c r="AM33" s="10"/>
+      <c r="AN33" s="10"/>
+      <c r="AO33" s="10"/>
+      <c r="AP33" s="10"/>
+      <c r="AQ33" s="10"/>
+      <c r="AR33" s="10"/>
+      <c r="AS33" s="10"/>
+      <c r="AT33" s="10"/>
+      <c r="AU33" s="10"/>
+      <c r="AV33" s="10"/>
+      <c r="AW33" s="10"/>
+      <c r="AX33" s="10"/>
+      <c r="AY33" s="10"/>
+      <c r="AZ33" s="10"/>
+      <c r="BA33" s="10"/>
+      <c r="BB33" s="10"/>
+      <c r="BC33" s="10"/>
+      <c r="BD33" s="10"/>
+      <c r="BE33" s="10"/>
+      <c r="BF33" s="10"/>
+      <c r="BG33" s="10"/>
+      <c r="BH33" s="10"/>
+      <c r="BI33" s="10"/>
+      <c r="BJ33" s="10"/>
+      <c r="BK33" s="10"/>
+      <c r="BL33" s="10"/>
+      <c r="BM33" s="10"/>
+      <c r="BN33" s="10"/>
+      <c r="BO33" s="10"/>
+    </row>
+    <row r="34" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="10"/>
+      <c r="AC34" s="10"/>
+      <c r="AD34" s="10"/>
+      <c r="AE34" s="10"/>
+      <c r="AF34" s="10"/>
+      <c r="AG34" s="10"/>
+      <c r="AH34" s="10"/>
+      <c r="AI34" s="10"/>
+      <c r="AJ34" s="10"/>
+      <c r="AK34" s="10"/>
+      <c r="AL34" s="10"/>
+      <c r="AM34" s="10"/>
+      <c r="AN34" s="10"/>
+      <c r="AO34" s="10"/>
+      <c r="AP34" s="10"/>
+      <c r="AQ34" s="10"/>
+      <c r="AR34" s="10"/>
+      <c r="AS34" s="10"/>
+      <c r="AT34" s="10"/>
+      <c r="AU34" s="10"/>
+      <c r="AV34" s="10"/>
+      <c r="AW34" s="10"/>
+      <c r="AX34" s="10"/>
+      <c r="AY34" s="10"/>
+      <c r="AZ34" s="10"/>
+      <c r="BA34" s="10"/>
+      <c r="BB34" s="10"/>
+      <c r="BC34" s="10"/>
+      <c r="BD34" s="10"/>
+      <c r="BE34" s="10"/>
+      <c r="BF34" s="10"/>
+      <c r="BG34" s="10"/>
+      <c r="BH34" s="10"/>
+      <c r="BI34" s="10"/>
+      <c r="BJ34" s="10"/>
+      <c r="BK34" s="10"/>
+      <c r="BL34" s="10"/>
+      <c r="BM34" s="10"/>
+      <c r="BN34" s="10"/>
+      <c r="BO34" s="10"/>
+    </row>
+    <row r="35" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="10"/>
+      <c r="AC35" s="10"/>
+      <c r="AD35" s="10"/>
+      <c r="AE35" s="10"/>
+      <c r="AF35" s="10"/>
+      <c r="AG35" s="10"/>
+      <c r="AH35" s="10"/>
+      <c r="AI35" s="10"/>
+      <c r="AJ35" s="10"/>
+      <c r="AK35" s="10"/>
+      <c r="AL35" s="10"/>
+      <c r="AM35" s="10"/>
+      <c r="AN35" s="10"/>
+      <c r="AO35" s="10"/>
+      <c r="AP35" s="10"/>
+      <c r="AQ35" s="10"/>
+      <c r="AR35" s="10"/>
+      <c r="AS35" s="10"/>
+      <c r="AT35" s="10"/>
+      <c r="AU35" s="10"/>
+      <c r="AV35" s="10"/>
+      <c r="AW35" s="10"/>
+      <c r="AX35" s="10"/>
+      <c r="AY35" s="10"/>
+      <c r="AZ35" s="10"/>
+      <c r="BA35" s="10"/>
+      <c r="BB35" s="10"/>
+      <c r="BC35" s="10"/>
+      <c r="BD35" s="10"/>
+      <c r="BE35" s="10"/>
+      <c r="BF35" s="10"/>
+      <c r="BG35" s="10"/>
+      <c r="BH35" s="10"/>
+      <c r="BI35" s="10"/>
+      <c r="BJ35" s="10"/>
+      <c r="BK35" s="10"/>
+      <c r="BL35" s="10"/>
+      <c r="BM35" s="10"/>
+      <c r="BN35" s="10"/>
+      <c r="BO35" s="10"/>
+    </row>
+    <row r="37" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="2" t="s">
-        <v>35</v>
+    <row r="38" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3338,7 +3715,7 @@
     <mergeCell ref="AA2:AG2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="H5:BO30">
+  <conditionalFormatting sqref="H5:BO35">
     <cfRule type="expression" dxfId="9" priority="1">
       <formula>완료율</formula>
     </cfRule>
@@ -3364,7 +3741,7 @@
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:BO31">
+  <conditionalFormatting sqref="B36:BO36">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>TRUE</formula>
     </cfRule>

--- a/프로젝트관리.xlsx
+++ b/프로젝트관리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ra_react\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDD16A7-1877-4CBD-A8FB-BA5C322F4C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A3F51-CBD3-4F01-8047-071FD98CDFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="780" windowWidth="19230" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13530" yWindow="240" windowWidth="19230" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="프로젝트 플래너" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>오른쪽에서 강조 표시할 기간을 선택합니다.  그 다음, 차트를 설명하는 범례가 나옵니다.</t>
   </si>
@@ -174,10 +174,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>배포 및 README 작성(트러블슈팅)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>테스트 및 버그 수정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -222,14 +218,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Axios/TanStack-Query &amp; 웹소켓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>실시간 센서/생산 추이 차트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>실시간 대시보드(공장 통합 현황판)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -238,10 +226,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공통 UI(버튼,팝업창,input, table)  </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>실시간 데이터 모니터링</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -250,31 +234,71 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공장 도면 기반 위에 가동/정지 상태 시각화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MES 공정 및 시스템관리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>사용자 권한별(작업자/관리자) 접근 메뉴 제어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>디자인 애니메이션 추가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>사이드바,header,footer</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">레이아웃 및 theme 테마 및 전역 스타일 설정 </t>
+    <t xml:space="preserve">로그인 및 관리자모드 경로별 레이아웃 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">로그인 및 관리자모드 경로별 레이아웃 </t>
+    <t>레이아웃 &amp; 스타일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next.js/Vite 기반 초기 세팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>컬러 시스템 및 폰트, 공통 변수 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공통 UI(버튼,모달,input, table)  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Axios Interceptor 설정/TanStack-Query &amp; 웹소켓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가동 정지 경보 상태 실시간 아이콘 색상 변경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>클릭 시 상세 팝업 연결</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실시간 센서/생산 추이 차트(Chart.js, Recharts )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 시간대별 생산 수량 변화 및 설비 온도/진동 센서 데이터</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  - 데이터 페이징, 정렬, 필터링, 검색 구현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 권한별(작업자/관리자) 접근제한 수정버튼 제어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 갱신 시 반짝이는(Pulse) 효과 구현</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디자인 수정/애니메이션 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드 및 배포/ README 작성(트러블슈팅)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -286,7 +310,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -396,6 +420,14 @@
     <font>
       <sz val="11"/>
       <color theme="7" tint="0.39997558519241921"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3" tint="-0.249977111117893"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -593,7 +625,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,6 +760,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1138,11 +1173,11 @@
     <tabColor theme="7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BO42"/>
+  <dimension ref="B1:BO47"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="2" width="51" style="2" customWidth="1"/>
+    <col min="2" max="2" width="57.75" style="2" customWidth="1"/>
     <col min="3" max="6" width="15.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="1" customWidth="1"/>
@@ -1152,7 +1187,7 @@
   <sheetData>
     <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1">
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -1229,7 +1264,7 @@
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="12">
         <v>1</v>
@@ -1576,7 +1611,7 @@
     </row>
     <row r="5" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="36">
         <v>16</v>
@@ -1655,8 +1690,8 @@
       <c r="BO5" s="39"/>
     </row>
     <row r="6" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="2" t="s">
-        <v>39</v>
+      <c r="B6" s="45" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="5">
         <v>2</v>
@@ -1729,7 +1764,7 @@
     </row>
     <row r="7" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1798,7 +1833,7 @@
     </row>
     <row r="8" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1936,7 +1971,7 @@
     </row>
     <row r="10" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -2004,6 +2039,9 @@
       <c r="BO10" s="10"/>
     </row>
     <row r="11" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2069,90 +2107,78 @@
       <c r="BN11" s="10"/>
       <c r="BO11" s="10"/>
     </row>
-    <row r="12" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="36">
-        <v>3</v>
-      </c>
-      <c r="D12" s="36">
-        <v>3</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="39"/>
-      <c r="AU12" s="39"/>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="39"/>
-      <c r="AX12" s="39"/>
-      <c r="AY12" s="39"/>
-      <c r="AZ12" s="39"/>
-      <c r="BA12" s="39"/>
-      <c r="BB12" s="39"/>
-      <c r="BC12" s="39"/>
-      <c r="BD12" s="39"/>
-      <c r="BE12" s="39"/>
-      <c r="BF12" s="39"/>
-      <c r="BG12" s="39"/>
-      <c r="BH12" s="39"/>
-      <c r="BI12" s="39"/>
-      <c r="BJ12" s="39"/>
-      <c r="BK12" s="39"/>
-      <c r="BL12" s="39"/>
-      <c r="BM12" s="39"/>
-      <c r="BN12" s="39"/>
-      <c r="BO12" s="39"/>
+    <row r="12" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="10"/>
+      <c r="AO12" s="10"/>
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10"/>
+      <c r="AR12" s="10"/>
+      <c r="AS12" s="10"/>
+      <c r="AT12" s="10"/>
+      <c r="AU12" s="10"/>
+      <c r="AV12" s="10"/>
+      <c r="AW12" s="10"/>
+      <c r="AX12" s="10"/>
+      <c r="AY12" s="10"/>
+      <c r="AZ12" s="10"/>
+      <c r="BA12" s="10"/>
+      <c r="BB12" s="10"/>
+      <c r="BC12" s="10"/>
+      <c r="BD12" s="10"/>
+      <c r="BE12" s="10"/>
+      <c r="BF12" s="10"/>
+      <c r="BG12" s="10"/>
+      <c r="BH12" s="10"/>
+      <c r="BI12" s="10"/>
+      <c r="BJ12" s="10"/>
+      <c r="BK12" s="10"/>
+      <c r="BL12" s="10"/>
+      <c r="BM12" s="10"/>
+      <c r="BN12" s="10"/>
+      <c r="BO12" s="10"/>
     </row>
     <row r="13" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="5">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3</v>
-      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="H13" s="9"/>
@@ -2216,81 +2242,90 @@
       <c r="BN13" s="10"/>
       <c r="BO13" s="10"/>
     </row>
-    <row r="14" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
-      <c r="AF14" s="10"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="10"/>
-      <c r="AI14" s="10"/>
-      <c r="AJ14" s="10"/>
-      <c r="AK14" s="10"/>
-      <c r="AL14" s="10"/>
-      <c r="AM14" s="10"/>
-      <c r="AN14" s="10"/>
-      <c r="AO14" s="10"/>
-      <c r="AP14" s="10"/>
-      <c r="AQ14" s="10"/>
-      <c r="AR14" s="10"/>
-      <c r="AS14" s="10"/>
-      <c r="AT14" s="10"/>
-      <c r="AU14" s="10"/>
-      <c r="AV14" s="10"/>
-      <c r="AW14" s="10"/>
-      <c r="AX14" s="10"/>
-      <c r="AY14" s="10"/>
-      <c r="AZ14" s="10"/>
-      <c r="BA14" s="10"/>
-      <c r="BB14" s="10"/>
-      <c r="BC14" s="10"/>
-      <c r="BD14" s="10"/>
-      <c r="BE14" s="10"/>
-      <c r="BF14" s="10"/>
-      <c r="BG14" s="10"/>
-      <c r="BH14" s="10"/>
-      <c r="BI14" s="10"/>
-      <c r="BJ14" s="10"/>
-      <c r="BK14" s="10"/>
-      <c r="BL14" s="10"/>
-      <c r="BM14" s="10"/>
-      <c r="BN14" s="10"/>
-      <c r="BO14" s="10"/>
+    <row r="14" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="36">
+        <v>3</v>
+      </c>
+      <c r="D14" s="36">
+        <v>3</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="39"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="39"/>
+      <c r="AE14" s="39"/>
+      <c r="AF14" s="39"/>
+      <c r="AG14" s="39"/>
+      <c r="AH14" s="39"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="39"/>
+      <c r="AK14" s="39"/>
+      <c r="AL14" s="39"/>
+      <c r="AM14" s="39"/>
+      <c r="AN14" s="39"/>
+      <c r="AO14" s="39"/>
+      <c r="AP14" s="39"/>
+      <c r="AQ14" s="39"/>
+      <c r="AR14" s="39"/>
+      <c r="AS14" s="39"/>
+      <c r="AT14" s="39"/>
+      <c r="AU14" s="39"/>
+      <c r="AV14" s="39"/>
+      <c r="AW14" s="39"/>
+      <c r="AX14" s="39"/>
+      <c r="AY14" s="39"/>
+      <c r="AZ14" s="39"/>
+      <c r="BA14" s="39"/>
+      <c r="BB14" s="39"/>
+      <c r="BC14" s="39"/>
+      <c r="BD14" s="39"/>
+      <c r="BE14" s="39"/>
+      <c r="BF14" s="39"/>
+      <c r="BG14" s="39"/>
+      <c r="BH14" s="39"/>
+      <c r="BI14" s="39"/>
+      <c r="BJ14" s="39"/>
+      <c r="BK14" s="39"/>
+      <c r="BL14" s="39"/>
+      <c r="BM14" s="39"/>
+      <c r="BN14" s="39"/>
+      <c r="BO14" s="39"/>
     </row>
     <row r="15" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="H15" s="9"/>
@@ -2355,7 +2390,10 @@
       <c r="BO15" s="10"/>
     </row>
     <row r="16" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="6"/>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2420,79 +2458,78 @@
       <c r="BN16" s="10"/>
       <c r="BO16" s="10"/>
     </row>
-    <row r="17" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="39"/>
-      <c r="AD17" s="39"/>
-      <c r="AE17" s="39"/>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="39"/>
-      <c r="AH17" s="39"/>
-      <c r="AI17" s="39"/>
-      <c r="AJ17" s="39"/>
-      <c r="AK17" s="39"/>
-      <c r="AL17" s="39"/>
-      <c r="AM17" s="39"/>
-      <c r="AN17" s="39"/>
-      <c r="AO17" s="39"/>
-      <c r="AP17" s="39"/>
-      <c r="AQ17" s="39"/>
-      <c r="AR17" s="39"/>
-      <c r="AS17" s="39"/>
-      <c r="AT17" s="39"/>
-      <c r="AU17" s="39"/>
-      <c r="AV17" s="39"/>
-      <c r="AW17" s="39"/>
-      <c r="AX17" s="39"/>
-      <c r="AY17" s="39"/>
-      <c r="AZ17" s="39"/>
-      <c r="BA17" s="39"/>
-      <c r="BB17" s="39"/>
-      <c r="BC17" s="39"/>
-      <c r="BD17" s="39"/>
-      <c r="BE17" s="39"/>
-      <c r="BF17" s="39"/>
-      <c r="BG17" s="39"/>
-      <c r="BH17" s="39"/>
-      <c r="BI17" s="39"/>
-      <c r="BJ17" s="39"/>
-      <c r="BK17" s="39"/>
-      <c r="BL17" s="39"/>
-      <c r="BM17" s="39"/>
-      <c r="BN17" s="39"/>
-      <c r="BO17" s="39"/>
+    <row r="17" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="10"/>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+      <c r="AN17" s="10"/>
+      <c r="AO17" s="10"/>
+      <c r="AP17" s="10"/>
+      <c r="AQ17" s="10"/>
+      <c r="AR17" s="10"/>
+      <c r="AS17" s="10"/>
+      <c r="AT17" s="10"/>
+      <c r="AU17" s="10"/>
+      <c r="AV17" s="10"/>
+      <c r="AW17" s="10"/>
+      <c r="AX17" s="10"/>
+      <c r="AY17" s="10"/>
+      <c r="AZ17" s="10"/>
+      <c r="BA17" s="10"/>
+      <c r="BB17" s="10"/>
+      <c r="BC17" s="10"/>
+      <c r="BD17" s="10"/>
+      <c r="BE17" s="10"/>
+      <c r="BF17" s="10"/>
+      <c r="BG17" s="10"/>
+      <c r="BH17" s="10"/>
+      <c r="BI17" s="10"/>
+      <c r="BJ17" s="10"/>
+      <c r="BK17" s="10"/>
+      <c r="BL17" s="10"/>
+      <c r="BM17" s="10"/>
+      <c r="BN17" s="10"/>
+      <c r="BO17" s="10"/>
     </row>
     <row r="18" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -2561,9 +2598,9 @@
     </row>
     <row r="19" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -2628,78 +2665,79 @@
       <c r="BN19" s="10"/>
       <c r="BO19" s="10"/>
     </row>
-    <row r="20" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
-      <c r="AI20" s="10"/>
-      <c r="AJ20" s="10"/>
-      <c r="AK20" s="10"/>
-      <c r="AL20" s="10"/>
-      <c r="AM20" s="10"/>
-      <c r="AN20" s="10"/>
-      <c r="AO20" s="10"/>
-      <c r="AP20" s="10"/>
-      <c r="AQ20" s="10"/>
-      <c r="AR20" s="10"/>
-      <c r="AS20" s="10"/>
-      <c r="AT20" s="10"/>
-      <c r="AU20" s="10"/>
-      <c r="AV20" s="10"/>
-      <c r="AW20" s="10"/>
-      <c r="AX20" s="10"/>
-      <c r="AY20" s="10"/>
-      <c r="AZ20" s="10"/>
-      <c r="BA20" s="10"/>
-      <c r="BB20" s="10"/>
-      <c r="BC20" s="10"/>
-      <c r="BD20" s="10"/>
-      <c r="BE20" s="10"/>
-      <c r="BF20" s="10"/>
-      <c r="BG20" s="10"/>
-      <c r="BH20" s="10"/>
-      <c r="BI20" s="10"/>
-      <c r="BJ20" s="10"/>
-      <c r="BK20" s="10"/>
-      <c r="BL20" s="10"/>
-      <c r="BM20" s="10"/>
-      <c r="BN20" s="10"/>
-      <c r="BO20" s="10"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39"/>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="39"/>
+      <c r="AK20" s="39"/>
+      <c r="AL20" s="39"/>
+      <c r="AM20" s="39"/>
+      <c r="AN20" s="39"/>
+      <c r="AO20" s="39"/>
+      <c r="AP20" s="39"/>
+      <c r="AQ20" s="39"/>
+      <c r="AR20" s="39"/>
+      <c r="AS20" s="39"/>
+      <c r="AT20" s="39"/>
+      <c r="AU20" s="39"/>
+      <c r="AV20" s="39"/>
+      <c r="AW20" s="39"/>
+      <c r="AX20" s="39"/>
+      <c r="AY20" s="39"/>
+      <c r="AZ20" s="39"/>
+      <c r="BA20" s="39"/>
+      <c r="BB20" s="39"/>
+      <c r="BC20" s="39"/>
+      <c r="BD20" s="39"/>
+      <c r="BE20" s="39"/>
+      <c r="BF20" s="39"/>
+      <c r="BG20" s="39"/>
+      <c r="BH20" s="39"/>
+      <c r="BI20" s="39"/>
+      <c r="BJ20" s="39"/>
+      <c r="BK20" s="39"/>
+      <c r="BL20" s="39"/>
+      <c r="BM20" s="39"/>
+      <c r="BN20" s="39"/>
+      <c r="BO20" s="39"/>
     </row>
     <row r="21" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2767,6 +2805,9 @@
       <c r="BO21" s="10"/>
     </row>
     <row r="22" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -2832,79 +2873,78 @@
       <c r="BN22" s="10"/>
       <c r="BO22" s="10"/>
     </row>
-    <row r="23" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="38"/>
-      <c r="AA23" s="38"/>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="39"/>
-      <c r="AD23" s="39"/>
-      <c r="AE23" s="39"/>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="39"/>
-      <c r="AH23" s="39"/>
-      <c r="AI23" s="39"/>
-      <c r="AJ23" s="39"/>
-      <c r="AK23" s="39"/>
-      <c r="AL23" s="39"/>
-      <c r="AM23" s="39"/>
-      <c r="AN23" s="39"/>
-      <c r="AO23" s="39"/>
-      <c r="AP23" s="39"/>
-      <c r="AQ23" s="39"/>
-      <c r="AR23" s="39"/>
-      <c r="AS23" s="39"/>
-      <c r="AT23" s="39"/>
-      <c r="AU23" s="39"/>
-      <c r="AV23" s="39"/>
-      <c r="AW23" s="39"/>
-      <c r="AX23" s="39"/>
-      <c r="AY23" s="39"/>
-      <c r="AZ23" s="39"/>
-      <c r="BA23" s="39"/>
-      <c r="BB23" s="39"/>
-      <c r="BC23" s="39"/>
-      <c r="BD23" s="39"/>
-      <c r="BE23" s="39"/>
-      <c r="BF23" s="39"/>
-      <c r="BG23" s="39"/>
-      <c r="BH23" s="39"/>
-      <c r="BI23" s="39"/>
-      <c r="BJ23" s="39"/>
-      <c r="BK23" s="39"/>
-      <c r="BL23" s="39"/>
-      <c r="BM23" s="39"/>
-      <c r="BN23" s="39"/>
-      <c r="BO23" s="39"/>
+    <row r="23" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="10"/>
+      <c r="AK23" s="10"/>
+      <c r="AL23" s="10"/>
+      <c r="AM23" s="10"/>
+      <c r="AN23" s="10"/>
+      <c r="AO23" s="10"/>
+      <c r="AP23" s="10"/>
+      <c r="AQ23" s="10"/>
+      <c r="AR23" s="10"/>
+      <c r="AS23" s="10"/>
+      <c r="AT23" s="10"/>
+      <c r="AU23" s="10"/>
+      <c r="AV23" s="10"/>
+      <c r="AW23" s="10"/>
+      <c r="AX23" s="10"/>
+      <c r="AY23" s="10"/>
+      <c r="AZ23" s="10"/>
+      <c r="BA23" s="10"/>
+      <c r="BB23" s="10"/>
+      <c r="BC23" s="10"/>
+      <c r="BD23" s="10"/>
+      <c r="BE23" s="10"/>
+      <c r="BF23" s="10"/>
+      <c r="BG23" s="10"/>
+      <c r="BH23" s="10"/>
+      <c r="BI23" s="10"/>
+      <c r="BJ23" s="10"/>
+      <c r="BK23" s="10"/>
+      <c r="BL23" s="10"/>
+      <c r="BM23" s="10"/>
+      <c r="BN23" s="10"/>
+      <c r="BO23" s="10"/>
     </row>
     <row r="24" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2973,7 +3013,7 @@
     </row>
     <row r="25" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -3108,7 +3148,7 @@
     </row>
     <row r="27" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -3178,7 +3218,7 @@
     </row>
     <row r="28" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -3247,7 +3287,7 @@
     </row>
     <row r="29" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3315,6 +3355,9 @@
       <c r="BO29" s="10"/>
     </row>
     <row r="30" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -3380,103 +3423,146 @@
       <c r="BN30" s="10"/>
       <c r="BO30" s="10"/>
     </row>
-    <row r="31" spans="2:67" s="44" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="43"/>
-      <c r="Y31" s="43"/>
-      <c r="Z31" s="43"/>
-      <c r="AA31" s="43"/>
-    </row>
-    <row r="32" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
-      <c r="AB32" s="10"/>
-      <c r="AC32" s="10"/>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="10"/>
-      <c r="AF32" s="10"/>
-      <c r="AG32" s="10"/>
-      <c r="AH32" s="10"/>
-      <c r="AI32" s="10"/>
-      <c r="AJ32" s="10"/>
-      <c r="AK32" s="10"/>
-      <c r="AL32" s="10"/>
-      <c r="AM32" s="10"/>
-      <c r="AN32" s="10"/>
-      <c r="AO32" s="10"/>
-      <c r="AP32" s="10"/>
-      <c r="AQ32" s="10"/>
-      <c r="AR32" s="10"/>
-      <c r="AS32" s="10"/>
-      <c r="AT32" s="10"/>
-      <c r="AU32" s="10"/>
-      <c r="AV32" s="10"/>
-      <c r="AW32" s="10"/>
-      <c r="AX32" s="10"/>
-      <c r="AY32" s="10"/>
-      <c r="AZ32" s="10"/>
-      <c r="BA32" s="10"/>
-      <c r="BB32" s="10"/>
-      <c r="BC32" s="10"/>
-      <c r="BD32" s="10"/>
-      <c r="BE32" s="10"/>
-      <c r="BF32" s="10"/>
-      <c r="BG32" s="10"/>
-      <c r="BH32" s="10"/>
-      <c r="BI32" s="10"/>
-      <c r="BJ32" s="10"/>
-      <c r="BK32" s="10"/>
-      <c r="BL32" s="10"/>
-      <c r="BM32" s="10"/>
-      <c r="BN32" s="10"/>
-      <c r="BO32" s="10"/>
+    <row r="31" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10"/>
+      <c r="AE31" s="10"/>
+      <c r="AF31" s="10"/>
+      <c r="AG31" s="10"/>
+      <c r="AH31" s="10"/>
+      <c r="AI31" s="10"/>
+      <c r="AJ31" s="10"/>
+      <c r="AK31" s="10"/>
+      <c r="AL31" s="10"/>
+      <c r="AM31" s="10"/>
+      <c r="AN31" s="10"/>
+      <c r="AO31" s="10"/>
+      <c r="AP31" s="10"/>
+      <c r="AQ31" s="10"/>
+      <c r="AR31" s="10"/>
+      <c r="AS31" s="10"/>
+      <c r="AT31" s="10"/>
+      <c r="AU31" s="10"/>
+      <c r="AV31" s="10"/>
+      <c r="AW31" s="10"/>
+      <c r="AX31" s="10"/>
+      <c r="AY31" s="10"/>
+      <c r="AZ31" s="10"/>
+      <c r="BA31" s="10"/>
+      <c r="BB31" s="10"/>
+      <c r="BC31" s="10"/>
+      <c r="BD31" s="10"/>
+      <c r="BE31" s="10"/>
+      <c r="BF31" s="10"/>
+      <c r="BG31" s="10"/>
+      <c r="BH31" s="10"/>
+      <c r="BI31" s="10"/>
+      <c r="BJ31" s="10"/>
+      <c r="BK31" s="10"/>
+      <c r="BL31" s="10"/>
+      <c r="BM31" s="10"/>
+      <c r="BN31" s="10"/>
+      <c r="BO31" s="10"/>
+    </row>
+    <row r="32" spans="2:67" s="40" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="39"/>
+      <c r="AC32" s="39"/>
+      <c r="AD32" s="39"/>
+      <c r="AE32" s="39"/>
+      <c r="AF32" s="39"/>
+      <c r="AG32" s="39"/>
+      <c r="AH32" s="39"/>
+      <c r="AI32" s="39"/>
+      <c r="AJ32" s="39"/>
+      <c r="AK32" s="39"/>
+      <c r="AL32" s="39"/>
+      <c r="AM32" s="39"/>
+      <c r="AN32" s="39"/>
+      <c r="AO32" s="39"/>
+      <c r="AP32" s="39"/>
+      <c r="AQ32" s="39"/>
+      <c r="AR32" s="39"/>
+      <c r="AS32" s="39"/>
+      <c r="AT32" s="39"/>
+      <c r="AU32" s="39"/>
+      <c r="AV32" s="39"/>
+      <c r="AW32" s="39"/>
+      <c r="AX32" s="39"/>
+      <c r="AY32" s="39"/>
+      <c r="AZ32" s="39"/>
+      <c r="BA32" s="39"/>
+      <c r="BB32" s="39"/>
+      <c r="BC32" s="39"/>
+      <c r="BD32" s="39"/>
+      <c r="BE32" s="39"/>
+      <c r="BF32" s="39"/>
+      <c r="BG32" s="39"/>
+      <c r="BH32" s="39"/>
+      <c r="BI32" s="39"/>
+      <c r="BJ32" s="39"/>
+      <c r="BK32" s="39"/>
+      <c r="BL32" s="39"/>
+      <c r="BM32" s="39"/>
+      <c r="BN32" s="39"/>
+      <c r="BO32" s="39"/>
     </row>
     <row r="33" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -3543,6 +3629,9 @@
       <c r="BO33" s="10"/>
     </row>
     <row r="34" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -3674,29 +3763,323 @@
       <c r="BN35" s="10"/>
       <c r="BO35" s="10"/>
     </row>
-    <row r="37" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="2" t="s">
-        <v>19</v>
-      </c>
+    <row r="36" spans="2:67" s="44" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="43"/>
+      <c r="Y36" s="43"/>
+      <c r="Z36" s="43"/>
+      <c r="AA36" s="43"/>
+    </row>
+    <row r="37" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="10"/>
+      <c r="AC37" s="10"/>
+      <c r="AD37" s="10"/>
+      <c r="AE37" s="10"/>
+      <c r="AF37" s="10"/>
+      <c r="AG37" s="10"/>
+      <c r="AH37" s="10"/>
+      <c r="AI37" s="10"/>
+      <c r="AJ37" s="10"/>
+      <c r="AK37" s="10"/>
+      <c r="AL37" s="10"/>
+      <c r="AM37" s="10"/>
+      <c r="AN37" s="10"/>
+      <c r="AO37" s="10"/>
+      <c r="AP37" s="10"/>
+      <c r="AQ37" s="10"/>
+      <c r="AR37" s="10"/>
+      <c r="AS37" s="10"/>
+      <c r="AT37" s="10"/>
+      <c r="AU37" s="10"/>
+      <c r="AV37" s="10"/>
+      <c r="AW37" s="10"/>
+      <c r="AX37" s="10"/>
+      <c r="AY37" s="10"/>
+      <c r="AZ37" s="10"/>
+      <c r="BA37" s="10"/>
+      <c r="BB37" s="10"/>
+      <c r="BC37" s="10"/>
+      <c r="BD37" s="10"/>
+      <c r="BE37" s="10"/>
+      <c r="BF37" s="10"/>
+      <c r="BG37" s="10"/>
+      <c r="BH37" s="10"/>
+      <c r="BI37" s="10"/>
+      <c r="BJ37" s="10"/>
+      <c r="BK37" s="10"/>
+      <c r="BL37" s="10"/>
+      <c r="BM37" s="10"/>
+      <c r="BN37" s="10"/>
+      <c r="BO37" s="10"/>
+    </row>
+    <row r="38" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="10"/>
+      <c r="AC38" s="10"/>
+      <c r="AD38" s="10"/>
+      <c r="AE38" s="10"/>
+      <c r="AF38" s="10"/>
+      <c r="AG38" s="10"/>
+      <c r="AH38" s="10"/>
+      <c r="AI38" s="10"/>
+      <c r="AJ38" s="10"/>
+      <c r="AK38" s="10"/>
+      <c r="AL38" s="10"/>
+      <c r="AM38" s="10"/>
+      <c r="AN38" s="10"/>
+      <c r="AO38" s="10"/>
+      <c r="AP38" s="10"/>
+      <c r="AQ38" s="10"/>
+      <c r="AR38" s="10"/>
+      <c r="AS38" s="10"/>
+      <c r="AT38" s="10"/>
+      <c r="AU38" s="10"/>
+      <c r="AV38" s="10"/>
+      <c r="AW38" s="10"/>
+      <c r="AX38" s="10"/>
+      <c r="AY38" s="10"/>
+      <c r="AZ38" s="10"/>
+      <c r="BA38" s="10"/>
+      <c r="BB38" s="10"/>
+      <c r="BC38" s="10"/>
+      <c r="BD38" s="10"/>
+      <c r="BE38" s="10"/>
+      <c r="BF38" s="10"/>
+      <c r="BG38" s="10"/>
+      <c r="BH38" s="10"/>
+      <c r="BI38" s="10"/>
+      <c r="BJ38" s="10"/>
+      <c r="BK38" s="10"/>
+      <c r="BL38" s="10"/>
+      <c r="BM38" s="10"/>
+      <c r="BN38" s="10"/>
+      <c r="BO38" s="10"/>
+    </row>
+    <row r="39" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="10"/>
+      <c r="AC39" s="10"/>
+      <c r="AD39" s="10"/>
+      <c r="AE39" s="10"/>
+      <c r="AF39" s="10"/>
+      <c r="AG39" s="10"/>
+      <c r="AH39" s="10"/>
+      <c r="AI39" s="10"/>
+      <c r="AJ39" s="10"/>
+      <c r="AK39" s="10"/>
+      <c r="AL39" s="10"/>
+      <c r="AM39" s="10"/>
+      <c r="AN39" s="10"/>
+      <c r="AO39" s="10"/>
+      <c r="AP39" s="10"/>
+      <c r="AQ39" s="10"/>
+      <c r="AR39" s="10"/>
+      <c r="AS39" s="10"/>
+      <c r="AT39" s="10"/>
+      <c r="AU39" s="10"/>
+      <c r="AV39" s="10"/>
+      <c r="AW39" s="10"/>
+      <c r="AX39" s="10"/>
+      <c r="AY39" s="10"/>
+      <c r="AZ39" s="10"/>
+      <c r="BA39" s="10"/>
+      <c r="BB39" s="10"/>
+      <c r="BC39" s="10"/>
+      <c r="BD39" s="10"/>
+      <c r="BE39" s="10"/>
+      <c r="BF39" s="10"/>
+      <c r="BG39" s="10"/>
+      <c r="BH39" s="10"/>
+      <c r="BI39" s="10"/>
+      <c r="BJ39" s="10"/>
+      <c r="BK39" s="10"/>
+      <c r="BL39" s="10"/>
+      <c r="BM39" s="10"/>
+      <c r="BN39" s="10"/>
+      <c r="BO39" s="10"/>
+    </row>
+    <row r="40" spans="2:67" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="10"/>
+      <c r="AC40" s="10"/>
+      <c r="AD40" s="10"/>
+      <c r="AE40" s="10"/>
+      <c r="AF40" s="10"/>
+      <c r="AG40" s="10"/>
+      <c r="AH40" s="10"/>
+      <c r="AI40" s="10"/>
+      <c r="AJ40" s="10"/>
+      <c r="AK40" s="10"/>
+      <c r="AL40" s="10"/>
+      <c r="AM40" s="10"/>
+      <c r="AN40" s="10"/>
+      <c r="AO40" s="10"/>
+      <c r="AP40" s="10"/>
+      <c r="AQ40" s="10"/>
+      <c r="AR40" s="10"/>
+      <c r="AS40" s="10"/>
+      <c r="AT40" s="10"/>
+      <c r="AU40" s="10"/>
+      <c r="AV40" s="10"/>
+      <c r="AW40" s="10"/>
+      <c r="AX40" s="10"/>
+      <c r="AY40" s="10"/>
+      <c r="AZ40" s="10"/>
+      <c r="BA40" s="10"/>
+      <c r="BB40" s="10"/>
+      <c r="BC40" s="10"/>
+      <c r="BD40" s="10"/>
+      <c r="BE40" s="10"/>
+      <c r="BF40" s="10"/>
+      <c r="BG40" s="10"/>
+      <c r="BH40" s="10"/>
+      <c r="BI40" s="10"/>
+      <c r="BJ40" s="10"/>
+      <c r="BK40" s="10"/>
+      <c r="BL40" s="10"/>
+      <c r="BM40" s="10"/>
+      <c r="BN40" s="10"/>
+      <c r="BO40" s="10"/>
     </row>
     <row r="42" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3715,7 +4098,7 @@
     <mergeCell ref="AA2:AG2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="H5:BO35">
+  <conditionalFormatting sqref="H5:BO40">
     <cfRule type="expression" dxfId="9" priority="1">
       <formula>완료율</formula>
     </cfRule>
@@ -3741,7 +4124,7 @@
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36:BO36">
+  <conditionalFormatting sqref="B41:BO41">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>TRUE</formula>
     </cfRule>
